--- a/docs/questionnaire-scope-map.xlsx
+++ b/docs/questionnaire-scope-map.xlsx
@@ -418,7 +418,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Generated 2026-09-19 by scripts/build-question-scope-map.mjs</v>
+        <v>Generated 2026-09-21 by scripts/build-question-scope-map.mjs</v>
       </c>
     </row>
     <row r="4">
@@ -1582,7 +1582,7 @@
         <v>Yes when shown</v>
       </c>
       <c r="H17" t="str">
-        <v>Hidden for External Works (single rate column); Basic option hidden for New Build / Extension</v>
+        <v>Hidden for External works only (single rate column); Basic option hidden for New Build / Extension</v>
       </c>
       <c r="I17" t="str">
         <v>page.jsx:1572</v>
@@ -3867,7 +3867,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:S39"/>
   <cols>
     <col min="1" max="1" width="9.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -3880,16 +3880,14 @@
     <col min="9" max="9" width="15.83203125" customWidth="1"/>
     <col min="10" max="10" width="15.83203125" customWidth="1"/>
     <col min="11" max="11" width="15.83203125" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" customWidth="1"/>
-    <col min="13" max="13" width="3.83203125" customWidth="1"/>
+    <col min="12" max="12" width="3.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
     <col min="14" max="14" width="15.83203125" customWidth="1"/>
     <col min="15" max="15" width="15.83203125" customWidth="1"/>
     <col min="16" max="16" width="15.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="15.83203125" customWidth="1"/>
     <col min="19" max="19" width="15.83203125" customWidth="1"/>
-    <col min="20" max="20" width="15.83203125" customWidth="1"/>
-    <col min="21" max="21" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3909,31 +3907,31 @@
         <v>TODAY: New Build</v>
       </c>
       <c r="F1" t="str">
+        <v>TODAY: Extension</v>
+      </c>
+      <c r="G1" t="str">
         <v>TODAY: Refurbishment</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>TODAY: Fit-out</v>
       </c>
-      <c r="H1" t="str">
-        <v>TODAY: Extension</v>
-      </c>
       <c r="I1" t="str">
-        <v>TODAY: External Works</v>
+        <v>TODAY: External works only</v>
       </c>
       <c r="J1" t="str">
-        <v>TODAY: Renewable Energy</v>
+        <v>TODAY: Demolition only</v>
       </c>
       <c r="K1" t="str">
-        <v>TODAY: Demolition</v>
+        <v>TODAY: Other or mixed</v>
       </c>
       <c r="L1" t="str">
-        <v>TODAY: Mixed</v>
+        <v/>
       </c>
       <c r="M1" t="str">
-        <v/>
+        <v>TARGET: New Build</v>
       </c>
       <c r="N1" t="str">
-        <v>TARGET: New Build</v>
+        <v>TARGET: Extension</v>
       </c>
       <c r="O1" t="str">
         <v>TARGET: Refurbishment</v>
@@ -3942,19 +3940,13 @@
         <v>TARGET: Fit-out</v>
       </c>
       <c r="Q1" t="str">
-        <v>TARGET: Extension</v>
+        <v>TARGET: External works only</v>
       </c>
       <c r="R1" t="str">
-        <v>TARGET: External Works</v>
+        <v>TARGET: Demolition only</v>
       </c>
       <c r="S1" t="str">
-        <v>TARGET: Renewable Energy</v>
-      </c>
-      <c r="T1" t="str">
-        <v>TARGET: Demolition</v>
-      </c>
-      <c r="U1" t="str">
-        <v>TARGET: Mixed</v>
+        <v>TARGET: Other or mixed</v>
       </c>
     </row>
     <row r="2">
@@ -3992,7 +3984,7 @@
         <v>Show</v>
       </c>
       <c r="L2" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -4013,12 +4005,6 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
-      <c r="U2" t="str">
         <v/>
       </c>
     </row>
@@ -4057,7 +4043,7 @@
         <v>Show</v>
       </c>
       <c r="L3" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -4078,12 +4064,6 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
-      <c r="U3" t="str">
         <v/>
       </c>
     </row>
@@ -4122,7 +4102,7 @@
         <v>Show</v>
       </c>
       <c r="L4" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -4143,12 +4123,6 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v/>
-      </c>
-      <c r="U4" t="str">
         <v/>
       </c>
     </row>
@@ -4187,7 +4161,7 @@
         <v>Show</v>
       </c>
       <c r="L5" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -4208,12 +4182,6 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
         <v/>
       </c>
     </row>
@@ -4237,10 +4205,10 @@
         <v>Show</v>
       </c>
       <c r="G6" t="str">
+        <v>Show</v>
+      </c>
+      <c r="H6" t="str">
         <v>Hidden</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Show</v>
       </c>
       <c r="I6" t="str">
         <v>Hidden</v>
@@ -4252,7 +4220,7 @@
         <v>Hidden</v>
       </c>
       <c r="L6" t="str">
-        <v>Hidden</v>
+        <v/>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -4273,12 +4241,6 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
-      <c r="U6" t="str">
         <v/>
       </c>
     </row>
@@ -4317,7 +4279,7 @@
         <v>Show</v>
       </c>
       <c r="L7" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -4338,12 +4300,6 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-      <c r="U7" t="str">
         <v/>
       </c>
     </row>
@@ -4382,7 +4338,7 @@
         <v>Show</v>
       </c>
       <c r="L8" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -4403,12 +4359,6 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v/>
-      </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
-      <c r="U8" t="str">
         <v/>
       </c>
     </row>
@@ -4447,7 +4397,7 @@
         <v>Show</v>
       </c>
       <c r="L9" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -4468,12 +4418,6 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v/>
-      </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-      <c r="U9" t="str">
         <v/>
       </c>
     </row>
@@ -4512,7 +4456,7 @@
         <v>Show</v>
       </c>
       <c r="L10" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -4533,12 +4477,6 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-      <c r="U10" t="str">
         <v/>
       </c>
     </row>
@@ -4577,7 +4515,7 @@
         <v>Show</v>
       </c>
       <c r="L11" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -4598,12 +4536,6 @@
         <v/>
       </c>
       <c r="S11" t="str">
-        <v/>
-      </c>
-      <c r="T11" t="str">
-        <v/>
-      </c>
-      <c r="U11" t="str">
         <v/>
       </c>
     </row>
@@ -4642,7 +4574,7 @@
         <v>Hidden</v>
       </c>
       <c r="L12" t="str">
-        <v>Hidden</v>
+        <v/>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -4663,12 +4595,6 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <v/>
-      </c>
-      <c r="T12" t="str">
-        <v/>
-      </c>
-      <c r="U12" t="str">
         <v/>
       </c>
     </row>
@@ -4707,7 +4633,7 @@
         <v>Show</v>
       </c>
       <c r="L13" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -4728,12 +4654,6 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <v/>
-      </c>
-      <c r="T13" t="str">
-        <v/>
-      </c>
-      <c r="U13" t="str">
         <v/>
       </c>
     </row>
@@ -4772,7 +4692,7 @@
         <v>Show</v>
       </c>
       <c r="L14" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -4793,12 +4713,6 @@
         <v/>
       </c>
       <c r="S14" t="str">
-        <v/>
-      </c>
-      <c r="T14" t="str">
-        <v/>
-      </c>
-      <c r="U14" t="str">
         <v/>
       </c>
     </row>
@@ -4837,7 +4751,7 @@
         <v>Show</v>
       </c>
       <c r="L15" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -4858,12 +4772,6 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v/>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-      <c r="U15" t="str">
         <v/>
       </c>
     </row>
@@ -4902,7 +4810,7 @@
         <v>Show</v>
       </c>
       <c r="L16" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -4923,12 +4831,6 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <v/>
-      </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-      <c r="U16" t="str">
         <v/>
       </c>
     </row>
@@ -4967,7 +4869,7 @@
         <v>Show</v>
       </c>
       <c r="L17" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -4988,12 +4890,6 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v/>
-      </c>
-      <c r="T17" t="str">
-        <v/>
-      </c>
-      <c r="U17" t="str">
         <v/>
       </c>
     </row>
@@ -5032,7 +4928,7 @@
         <v>Show</v>
       </c>
       <c r="L18" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -5053,12 +4949,6 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v/>
-      </c>
-      <c r="T18" t="str">
-        <v/>
-      </c>
-      <c r="U18" t="str">
         <v/>
       </c>
     </row>
@@ -5097,7 +4987,7 @@
         <v>Show</v>
       </c>
       <c r="L19" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -5118,12 +5008,6 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <v/>
-      </c>
-      <c r="T19" t="str">
-        <v/>
-      </c>
-      <c r="U19" t="str">
         <v/>
       </c>
     </row>
@@ -5162,7 +5046,7 @@
         <v>Show</v>
       </c>
       <c r="L20" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -5183,12 +5067,6 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <v/>
-      </c>
-      <c r="T20" t="str">
-        <v/>
-      </c>
-      <c r="U20" t="str">
         <v/>
       </c>
     </row>
@@ -5227,7 +5105,7 @@
         <v>Show</v>
       </c>
       <c r="L21" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -5248,12 +5126,6 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v/>
-      </c>
-      <c r="T21" t="str">
-        <v/>
-      </c>
-      <c r="U21" t="str">
         <v/>
       </c>
     </row>
@@ -5292,7 +5164,7 @@
         <v>Show</v>
       </c>
       <c r="L22" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -5313,12 +5185,6 @@
         <v/>
       </c>
       <c r="S22" t="str">
-        <v/>
-      </c>
-      <c r="T22" t="str">
-        <v/>
-      </c>
-      <c r="U22" t="str">
         <v/>
       </c>
     </row>
@@ -5357,7 +5223,7 @@
         <v>Show</v>
       </c>
       <c r="L23" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -5378,12 +5244,6 @@
         <v/>
       </c>
       <c r="S23" t="str">
-        <v/>
-      </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-      <c r="U23" t="str">
         <v/>
       </c>
     </row>
@@ -5422,7 +5282,7 @@
         <v>Show</v>
       </c>
       <c r="L24" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -5443,12 +5303,6 @@
         <v/>
       </c>
       <c r="S24" t="str">
-        <v/>
-      </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-      <c r="U24" t="str">
         <v/>
       </c>
     </row>
@@ -5487,7 +5341,7 @@
         <v>Show</v>
       </c>
       <c r="L25" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -5508,12 +5362,6 @@
         <v/>
       </c>
       <c r="S25" t="str">
-        <v/>
-      </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-      <c r="U25" t="str">
         <v/>
       </c>
     </row>
@@ -5552,7 +5400,7 @@
         <v>Show</v>
       </c>
       <c r="L26" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -5573,12 +5421,6 @@
         <v/>
       </c>
       <c r="S26" t="str">
-        <v/>
-      </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-      <c r="U26" t="str">
         <v/>
       </c>
     </row>
@@ -5617,7 +5459,7 @@
         <v>Show</v>
       </c>
       <c r="L27" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -5638,12 +5480,6 @@
         <v/>
       </c>
       <c r="S27" t="str">
-        <v/>
-      </c>
-      <c r="T27" t="str">
-        <v/>
-      </c>
-      <c r="U27" t="str">
         <v/>
       </c>
     </row>
@@ -5682,7 +5518,7 @@
         <v>Show</v>
       </c>
       <c r="L28" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -5703,12 +5539,6 @@
         <v/>
       </c>
       <c r="S28" t="str">
-        <v/>
-      </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-      <c r="U28" t="str">
         <v/>
       </c>
     </row>
@@ -5747,7 +5577,7 @@
         <v>Show</v>
       </c>
       <c r="L29" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -5768,12 +5598,6 @@
         <v/>
       </c>
       <c r="S29" t="str">
-        <v/>
-      </c>
-      <c r="T29" t="str">
-        <v/>
-      </c>
-      <c r="U29" t="str">
         <v/>
       </c>
     </row>
@@ -5812,7 +5636,7 @@
         <v>Show</v>
       </c>
       <c r="L30" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -5833,12 +5657,6 @@
         <v/>
       </c>
       <c r="S30" t="str">
-        <v/>
-      </c>
-      <c r="T30" t="str">
-        <v/>
-      </c>
-      <c r="U30" t="str">
         <v/>
       </c>
     </row>
@@ -5877,7 +5695,7 @@
         <v>Show</v>
       </c>
       <c r="L31" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -5898,12 +5716,6 @@
         <v/>
       </c>
       <c r="S31" t="str">
-        <v/>
-      </c>
-      <c r="T31" t="str">
-        <v/>
-      </c>
-      <c r="U31" t="str">
         <v/>
       </c>
     </row>
@@ -5942,7 +5754,7 @@
         <v>Show</v>
       </c>
       <c r="L32" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -5963,12 +5775,6 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v/>
-      </c>
-      <c r="T32" t="str">
-        <v/>
-      </c>
-      <c r="U32" t="str">
         <v/>
       </c>
     </row>
@@ -6007,7 +5813,7 @@
         <v>Show</v>
       </c>
       <c r="L33" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -6028,12 +5834,6 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <v/>
-      </c>
-      <c r="T33" t="str">
-        <v/>
-      </c>
-      <c r="U33" t="str">
         <v/>
       </c>
     </row>
@@ -6072,7 +5872,7 @@
         <v>Show</v>
       </c>
       <c r="L34" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -6093,12 +5893,6 @@
         <v/>
       </c>
       <c r="S34" t="str">
-        <v/>
-      </c>
-      <c r="T34" t="str">
-        <v/>
-      </c>
-      <c r="U34" t="str">
         <v/>
       </c>
     </row>
@@ -6137,7 +5931,7 @@
         <v>Show</v>
       </c>
       <c r="L35" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -6158,12 +5952,6 @@
         <v/>
       </c>
       <c r="S35" t="str">
-        <v/>
-      </c>
-      <c r="T35" t="str">
-        <v/>
-      </c>
-      <c r="U35" t="str">
         <v/>
       </c>
     </row>
@@ -6202,7 +5990,7 @@
         <v>Show</v>
       </c>
       <c r="L36" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -6223,12 +6011,6 @@
         <v/>
       </c>
       <c r="S36" t="str">
-        <v/>
-      </c>
-      <c r="T36" t="str">
-        <v/>
-      </c>
-      <c r="U36" t="str">
         <v/>
       </c>
     </row>
@@ -6267,7 +6049,7 @@
         <v>Show</v>
       </c>
       <c r="L37" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -6288,12 +6070,6 @@
         <v/>
       </c>
       <c r="S37" t="str">
-        <v/>
-      </c>
-      <c r="T37" t="str">
-        <v/>
-      </c>
-      <c r="U37" t="str">
         <v/>
       </c>
     </row>
@@ -6332,7 +6108,7 @@
         <v>Show</v>
       </c>
       <c r="L38" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -6353,12 +6129,6 @@
         <v/>
       </c>
       <c r="S38" t="str">
-        <v/>
-      </c>
-      <c r="T38" t="str">
-        <v/>
-      </c>
-      <c r="U38" t="str">
         <v/>
       </c>
     </row>
@@ -6397,7 +6167,7 @@
         <v>Show</v>
       </c>
       <c r="L39" t="str">
-        <v>Show</v>
+        <v/>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -6418,18 +6188,12 @@
         <v/>
       </c>
       <c r="S39" t="str">
-        <v/>
-      </c>
-      <c r="T39" t="str">
-        <v/>
-      </c>
-      <c r="U39" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U39"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S39"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12115,7 +11879,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U123"/>
+  <dimension ref="A1:S123"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="7.83203125" customWidth="1"/>
@@ -12128,16 +11892,14 @@
     <col min="9" max="9" width="18.83203125" customWidth="1"/>
     <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" customWidth="1"/>
-    <col min="13" max="13" width="3.83203125" customWidth="1"/>
+    <col min="12" max="12" width="3.83203125" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" customWidth="1"/>
     <col min="14" max="14" width="15.83203125" customWidth="1"/>
     <col min="15" max="15" width="15.83203125" customWidth="1"/>
     <col min="16" max="16" width="15.83203125" customWidth="1"/>
     <col min="17" max="17" width="15.83203125" customWidth="1"/>
     <col min="18" max="18" width="15.83203125" customWidth="1"/>
     <col min="19" max="19" width="15.83203125" customWidth="1"/>
-    <col min="20" max="20" width="15.83203125" customWidth="1"/>
-    <col min="21" max="21" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12157,31 +11919,31 @@
         <v>TODAY: New Build</v>
       </c>
       <c r="F1" t="str">
+        <v>TODAY: Extension</v>
+      </c>
+      <c r="G1" t="str">
         <v>TODAY: Refurbishment</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>TODAY: Fit-out</v>
       </c>
-      <c r="H1" t="str">
-        <v>TODAY: Extension</v>
-      </c>
       <c r="I1" t="str">
-        <v>TODAY: External Works</v>
+        <v>TODAY: External works only</v>
       </c>
       <c r="J1" t="str">
-        <v>TODAY: Renewable Energy</v>
+        <v>TODAY: Demolition only</v>
       </c>
       <c r="K1" t="str">
-        <v>TODAY: Demolition</v>
+        <v>TODAY: Other or mixed</v>
       </c>
       <c r="L1" t="str">
-        <v>TODAY: Mixed</v>
+        <v/>
       </c>
       <c r="M1" t="str">
-        <v/>
+        <v>TARGET: New Build</v>
       </c>
       <c r="N1" t="str">
-        <v>TARGET: New Build</v>
+        <v>TARGET: Extension</v>
       </c>
       <c r="O1" t="str">
         <v>TARGET: Refurbishment</v>
@@ -12190,19 +11952,13 @@
         <v>TARGET: Fit-out</v>
       </c>
       <c r="Q1" t="str">
-        <v>TARGET: Extension</v>
+        <v>TARGET: External works only</v>
       </c>
       <c r="R1" t="str">
-        <v>TARGET: External Works</v>
+        <v>TARGET: Demolition only</v>
       </c>
       <c r="S1" t="str">
-        <v>TARGET: Renewable Energy</v>
-      </c>
-      <c r="T1" t="str">
-        <v>TARGET: Demolition</v>
-      </c>
-      <c r="U1" t="str">
-        <v>TARGET: Mixed</v>
+        <v>TARGET: Other or mixed</v>
       </c>
     </row>
     <row r="2">
@@ -12225,22 +11981,22 @@
         <v>Shown</v>
       </c>
       <c r="G2" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H2" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I2" t="str">
         <v>Hidden — no rate</v>
       </c>
       <c r="J2" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="K2" t="str">
         <v>Shown</v>
       </c>
       <c r="L2" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -12261,12 +12017,6 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
-      <c r="U2" t="str">
         <v/>
       </c>
     </row>
@@ -12290,22 +12040,22 @@
         <v>Shown</v>
       </c>
       <c r="G3" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H3" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I3" t="str">
         <v>Shown</v>
       </c>
       <c r="J3" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="K3" t="str">
         <v>Shown</v>
       </c>
       <c r="L3" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -12326,12 +12076,6 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
-      <c r="U3" t="str">
         <v/>
       </c>
     </row>
@@ -12355,22 +12099,22 @@
         <v>Shown</v>
       </c>
       <c r="G4" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H4" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I4" t="str">
         <v>Shown</v>
       </c>
       <c r="J4" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="K4" t="str">
         <v>Shown</v>
       </c>
       <c r="L4" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -12391,12 +12135,6 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v/>
-      </c>
-      <c r="U4" t="str">
         <v/>
       </c>
     </row>
@@ -12417,25 +12155,25 @@
         <v>Shown</v>
       </c>
       <c r="F5" t="str">
+        <v>Shown</v>
+      </c>
+      <c r="G5" t="str">
         <v>Hidden — no rate</v>
       </c>
-      <c r="G5" t="str">
-        <v>Hidden — group off</v>
-      </c>
       <c r="H5" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I5" t="str">
         <v>Shown</v>
       </c>
       <c r="J5" t="str">
-        <v>Hidden — group off</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="K5" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="L5" t="str">
-        <v>Hidden — no rate</v>
+        <v/>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -12456,12 +12194,6 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
         <v/>
       </c>
     </row>
@@ -12482,25 +12214,25 @@
         <v>Hidden — no rate</v>
       </c>
       <c r="F6" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G6" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H6" t="str">
-        <v>Hidden — no rate</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I6" t="str">
         <v>Hidden — no rate</v>
       </c>
       <c r="J6" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="K6" t="str">
         <v>Shown</v>
       </c>
       <c r="L6" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -12521,12 +12253,6 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
-      <c r="U6" t="str">
         <v/>
       </c>
     </row>
@@ -12547,13 +12273,13 @@
         <v>Shown</v>
       </c>
       <c r="F7" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="G7" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="H7" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I7" t="str">
         <v>Hidden — group off</v>
@@ -12562,10 +12288,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K7" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L7" t="str">
-        <v>Hidden — no rate</v>
+        <v/>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -12586,12 +12312,6 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
-      <c r="U7" t="str">
         <v/>
       </c>
     </row>
@@ -12612,13 +12332,13 @@
         <v>Shown</v>
       </c>
       <c r="F8" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="G8" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="H8" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I8" t="str">
         <v>Hidden — group off</v>
@@ -12627,10 +12347,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K8" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L8" t="str">
-        <v>Hidden — no rate</v>
+        <v/>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -12651,12 +12371,6 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v/>
-      </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
-      <c r="U8" t="str">
         <v/>
       </c>
     </row>
@@ -12677,13 +12391,13 @@
         <v>Shown</v>
       </c>
       <c r="F9" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="G9" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="H9" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I9" t="str">
         <v>Hidden — group off</v>
@@ -12692,10 +12406,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K9" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L9" t="str">
-        <v>Hidden — no rate</v>
+        <v/>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -12716,12 +12430,6 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v/>
-      </c>
-      <c r="T9" t="str">
-        <v/>
-      </c>
-      <c r="U9" t="str">
         <v/>
       </c>
     </row>
@@ -12742,13 +12450,13 @@
         <v>Shown</v>
       </c>
       <c r="F10" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="G10" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="H10" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I10" t="str">
         <v>Hidden — group off</v>
@@ -12757,10 +12465,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K10" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L10" t="str">
-        <v>Hidden — no rate</v>
+        <v/>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -12781,12 +12489,6 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-      <c r="U10" t="str">
         <v/>
       </c>
     </row>
@@ -12810,10 +12512,10 @@
         <v>Shown</v>
       </c>
       <c r="G11" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H11" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I11" t="str">
         <v>Hidden — group off</v>
@@ -12822,10 +12524,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K11" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L11" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -12846,12 +12548,6 @@
         <v/>
       </c>
       <c r="S11" t="str">
-        <v/>
-      </c>
-      <c r="T11" t="str">
-        <v/>
-      </c>
-      <c r="U11" t="str">
         <v/>
       </c>
     </row>
@@ -12875,10 +12571,10 @@
         <v>Shown</v>
       </c>
       <c r="G12" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H12" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I12" t="str">
         <v>Hidden — group off</v>
@@ -12887,10 +12583,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K12" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L12" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -12911,12 +12607,6 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <v/>
-      </c>
-      <c r="T12" t="str">
-        <v/>
-      </c>
-      <c r="U12" t="str">
         <v/>
       </c>
     </row>
@@ -12940,10 +12630,10 @@
         <v>Shown</v>
       </c>
       <c r="G13" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H13" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I13" t="str">
         <v>Hidden — group off</v>
@@ -12952,10 +12642,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K13" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L13" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -12976,12 +12666,6 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <v/>
-      </c>
-      <c r="T13" t="str">
-        <v/>
-      </c>
-      <c r="U13" t="str">
         <v/>
       </c>
     </row>
@@ -13005,10 +12689,10 @@
         <v>Shown</v>
       </c>
       <c r="G14" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H14" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I14" t="str">
         <v>Hidden — group off</v>
@@ -13017,10 +12701,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K14" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L14" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -13041,12 +12725,6 @@
         <v/>
       </c>
       <c r="S14" t="str">
-        <v/>
-      </c>
-      <c r="T14" t="str">
-        <v/>
-      </c>
-      <c r="U14" t="str">
         <v/>
       </c>
     </row>
@@ -13070,10 +12748,10 @@
         <v>Shown</v>
       </c>
       <c r="G15" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H15" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I15" t="str">
         <v>Hidden — group off</v>
@@ -13082,10 +12760,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K15" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L15" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -13106,12 +12784,6 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v/>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
-      <c r="U15" t="str">
         <v/>
       </c>
     </row>
@@ -13135,10 +12807,10 @@
         <v>Shown</v>
       </c>
       <c r="G16" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H16" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I16" t="str">
         <v>Hidden — group off</v>
@@ -13147,10 +12819,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K16" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L16" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -13171,12 +12843,6 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <v/>
-      </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
-      <c r="U16" t="str">
         <v/>
       </c>
     </row>
@@ -13200,10 +12866,10 @@
         <v>Shown</v>
       </c>
       <c r="G17" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H17" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I17" t="str">
         <v>Hidden — group off</v>
@@ -13212,10 +12878,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K17" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L17" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -13236,12 +12902,6 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v/>
-      </c>
-      <c r="T17" t="str">
-        <v/>
-      </c>
-      <c r="U17" t="str">
         <v/>
       </c>
     </row>
@@ -13265,10 +12925,10 @@
         <v>Shown</v>
       </c>
       <c r="G18" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H18" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I18" t="str">
         <v>Hidden — group off</v>
@@ -13277,10 +12937,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K18" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L18" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -13301,12 +12961,6 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v/>
-      </c>
-      <c r="T18" t="str">
-        <v/>
-      </c>
-      <c r="U18" t="str">
         <v/>
       </c>
     </row>
@@ -13330,10 +12984,10 @@
         <v>Shown</v>
       </c>
       <c r="G19" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H19" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I19" t="str">
         <v>Hidden — group off</v>
@@ -13342,10 +12996,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K19" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L19" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -13366,12 +13020,6 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <v/>
-      </c>
-      <c r="T19" t="str">
-        <v/>
-      </c>
-      <c r="U19" t="str">
         <v/>
       </c>
     </row>
@@ -13407,10 +13055,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K20" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L20" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -13431,12 +13079,6 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <v/>
-      </c>
-      <c r="T20" t="str">
-        <v/>
-      </c>
-      <c r="U20" t="str">
         <v/>
       </c>
     </row>
@@ -13472,10 +13114,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K21" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L21" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -13496,12 +13138,6 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v/>
-      </c>
-      <c r="T21" t="str">
-        <v/>
-      </c>
-      <c r="U21" t="str">
         <v/>
       </c>
     </row>
@@ -13537,10 +13173,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K22" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L22" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -13561,12 +13197,6 @@
         <v/>
       </c>
       <c r="S22" t="str">
-        <v/>
-      </c>
-      <c r="T22" t="str">
-        <v/>
-      </c>
-      <c r="U22" t="str">
         <v/>
       </c>
     </row>
@@ -13602,10 +13232,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K23" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L23" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -13626,12 +13256,6 @@
         <v/>
       </c>
       <c r="S23" t="str">
-        <v/>
-      </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-      <c r="U23" t="str">
         <v/>
       </c>
     </row>
@@ -13667,10 +13291,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K24" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L24" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -13691,12 +13315,6 @@
         <v/>
       </c>
       <c r="S24" t="str">
-        <v/>
-      </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-      <c r="U24" t="str">
         <v/>
       </c>
     </row>
@@ -13732,10 +13350,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K25" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L25" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -13756,12 +13374,6 @@
         <v/>
       </c>
       <c r="S25" t="str">
-        <v/>
-      </c>
-      <c r="T25" t="str">
-        <v/>
-      </c>
-      <c r="U25" t="str">
         <v/>
       </c>
     </row>
@@ -13797,10 +13409,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K26" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L26" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M26" t="str">
         <v/>
@@ -13821,12 +13433,6 @@
         <v/>
       </c>
       <c r="S26" t="str">
-        <v/>
-      </c>
-      <c r="T26" t="str">
-        <v/>
-      </c>
-      <c r="U26" t="str">
         <v/>
       </c>
     </row>
@@ -13862,10 +13468,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K27" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L27" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -13886,12 +13492,6 @@
         <v/>
       </c>
       <c r="S27" t="str">
-        <v/>
-      </c>
-      <c r="T27" t="str">
-        <v/>
-      </c>
-      <c r="U27" t="str">
         <v/>
       </c>
     </row>
@@ -13927,10 +13527,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K28" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L28" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M28" t="str">
         <v/>
@@ -13951,12 +13551,6 @@
         <v/>
       </c>
       <c r="S28" t="str">
-        <v/>
-      </c>
-      <c r="T28" t="str">
-        <v/>
-      </c>
-      <c r="U28" t="str">
         <v/>
       </c>
     </row>
@@ -13992,10 +13586,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K29" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L29" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M29" t="str">
         <v/>
@@ -14016,12 +13610,6 @@
         <v/>
       </c>
       <c r="S29" t="str">
-        <v/>
-      </c>
-      <c r="T29" t="str">
-        <v/>
-      </c>
-      <c r="U29" t="str">
         <v/>
       </c>
     </row>
@@ -14057,10 +13645,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K30" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L30" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M30" t="str">
         <v/>
@@ -14081,12 +13669,6 @@
         <v/>
       </c>
       <c r="S30" t="str">
-        <v/>
-      </c>
-      <c r="T30" t="str">
-        <v/>
-      </c>
-      <c r="U30" t="str">
         <v/>
       </c>
     </row>
@@ -14122,10 +13704,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K31" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L31" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M31" t="str">
         <v/>
@@ -14146,12 +13728,6 @@
         <v/>
       </c>
       <c r="S31" t="str">
-        <v/>
-      </c>
-      <c r="T31" t="str">
-        <v/>
-      </c>
-      <c r="U31" t="str">
         <v/>
       </c>
     </row>
@@ -14187,10 +13763,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K32" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L32" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -14211,12 +13787,6 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v/>
-      </c>
-      <c r="T32" t="str">
-        <v/>
-      </c>
-      <c r="U32" t="str">
         <v/>
       </c>
     </row>
@@ -14252,10 +13822,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K33" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L33" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M33" t="str">
         <v/>
@@ -14276,12 +13846,6 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <v/>
-      </c>
-      <c r="T33" t="str">
-        <v/>
-      </c>
-      <c r="U33" t="str">
         <v/>
       </c>
     </row>
@@ -14317,10 +13881,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K34" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L34" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M34" t="str">
         <v/>
@@ -14341,12 +13905,6 @@
         <v/>
       </c>
       <c r="S34" t="str">
-        <v/>
-      </c>
-      <c r="T34" t="str">
-        <v/>
-      </c>
-      <c r="U34" t="str">
         <v/>
       </c>
     </row>
@@ -14367,13 +13925,13 @@
         <v>Shown</v>
       </c>
       <c r="F35" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G35" t="str">
         <v>Shown</v>
       </c>
       <c r="H35" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I35" t="str">
         <v>Hidden — group off</v>
@@ -14382,10 +13940,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K35" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L35" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M35" t="str">
         <v/>
@@ -14406,12 +13964,6 @@
         <v/>
       </c>
       <c r="S35" t="str">
-        <v/>
-      </c>
-      <c r="T35" t="str">
-        <v/>
-      </c>
-      <c r="U35" t="str">
         <v/>
       </c>
     </row>
@@ -14432,13 +13984,13 @@
         <v>Shown</v>
       </c>
       <c r="F36" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G36" t="str">
         <v>Shown</v>
       </c>
       <c r="H36" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I36" t="str">
         <v>Hidden — group off</v>
@@ -14447,10 +13999,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K36" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L36" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M36" t="str">
         <v/>
@@ -14471,12 +14023,6 @@
         <v/>
       </c>
       <c r="S36" t="str">
-        <v/>
-      </c>
-      <c r="T36" t="str">
-        <v/>
-      </c>
-      <c r="U36" t="str">
         <v/>
       </c>
     </row>
@@ -14497,13 +14043,13 @@
         <v>Shown</v>
       </c>
       <c r="F37" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G37" t="str">
         <v>Shown</v>
       </c>
       <c r="H37" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I37" t="str">
         <v>Hidden — group off</v>
@@ -14512,10 +14058,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K37" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L37" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M37" t="str">
         <v/>
@@ -14536,12 +14082,6 @@
         <v/>
       </c>
       <c r="S37" t="str">
-        <v/>
-      </c>
-      <c r="T37" t="str">
-        <v/>
-      </c>
-      <c r="U37" t="str">
         <v/>
       </c>
     </row>
@@ -14562,13 +14102,13 @@
         <v>Shown</v>
       </c>
       <c r="F38" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G38" t="str">
         <v>Shown</v>
       </c>
       <c r="H38" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I38" t="str">
         <v>Hidden — group off</v>
@@ -14577,10 +14117,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K38" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L38" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M38" t="str">
         <v/>
@@ -14601,12 +14141,6 @@
         <v/>
       </c>
       <c r="S38" t="str">
-        <v/>
-      </c>
-      <c r="T38" t="str">
-        <v/>
-      </c>
-      <c r="U38" t="str">
         <v/>
       </c>
     </row>
@@ -14627,13 +14161,13 @@
         <v>Shown</v>
       </c>
       <c r="F39" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G39" t="str">
         <v>Shown</v>
       </c>
       <c r="H39" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I39" t="str">
         <v>Hidden — group off</v>
@@ -14642,10 +14176,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K39" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L39" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M39" t="str">
         <v/>
@@ -14666,12 +14200,6 @@
         <v/>
       </c>
       <c r="S39" t="str">
-        <v/>
-      </c>
-      <c r="T39" t="str">
-        <v/>
-      </c>
-      <c r="U39" t="str">
         <v/>
       </c>
     </row>
@@ -14692,13 +14220,13 @@
         <v>Shown</v>
       </c>
       <c r="F40" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G40" t="str">
         <v>Shown</v>
       </c>
       <c r="H40" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I40" t="str">
         <v>Hidden — group off</v>
@@ -14707,10 +14235,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K40" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L40" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M40" t="str">
         <v/>
@@ -14731,12 +14259,6 @@
         <v/>
       </c>
       <c r="S40" t="str">
-        <v/>
-      </c>
-      <c r="T40" t="str">
-        <v/>
-      </c>
-      <c r="U40" t="str">
         <v/>
       </c>
     </row>
@@ -14772,10 +14294,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K41" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L41" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M41" t="str">
         <v/>
@@ -14796,12 +14318,6 @@
         <v/>
       </c>
       <c r="S41" t="str">
-        <v/>
-      </c>
-      <c r="T41" t="str">
-        <v/>
-      </c>
-      <c r="U41" t="str">
         <v/>
       </c>
     </row>
@@ -14822,13 +14338,13 @@
         <v>Shown</v>
       </c>
       <c r="F42" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G42" t="str">
         <v>Shown</v>
       </c>
       <c r="H42" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I42" t="str">
         <v>Hidden — group off</v>
@@ -14837,10 +14353,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K42" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L42" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M42" t="str">
         <v/>
@@ -14861,12 +14377,6 @@
         <v/>
       </c>
       <c r="S42" t="str">
-        <v/>
-      </c>
-      <c r="T42" t="str">
-        <v/>
-      </c>
-      <c r="U42" t="str">
         <v/>
       </c>
     </row>
@@ -14887,13 +14397,13 @@
         <v>Shown</v>
       </c>
       <c r="F43" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G43" t="str">
         <v>Shown</v>
       </c>
       <c r="H43" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I43" t="str">
         <v>Hidden — group off</v>
@@ -14902,10 +14412,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K43" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L43" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M43" t="str">
         <v/>
@@ -14926,12 +14436,6 @@
         <v/>
       </c>
       <c r="S43" t="str">
-        <v/>
-      </c>
-      <c r="T43" t="str">
-        <v/>
-      </c>
-      <c r="U43" t="str">
         <v/>
       </c>
     </row>
@@ -14952,13 +14456,13 @@
         <v>Shown</v>
       </c>
       <c r="F44" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G44" t="str">
         <v>Shown</v>
       </c>
       <c r="H44" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I44" t="str">
         <v>Hidden — group off</v>
@@ -14967,10 +14471,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K44" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L44" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M44" t="str">
         <v/>
@@ -14991,12 +14495,6 @@
         <v/>
       </c>
       <c r="S44" t="str">
-        <v/>
-      </c>
-      <c r="T44" t="str">
-        <v/>
-      </c>
-      <c r="U44" t="str">
         <v/>
       </c>
     </row>
@@ -15017,13 +14515,13 @@
         <v>Shown</v>
       </c>
       <c r="F45" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G45" t="str">
         <v>Shown</v>
       </c>
       <c r="H45" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I45" t="str">
         <v>Hidden — group off</v>
@@ -15032,10 +14530,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K45" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L45" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M45" t="str">
         <v/>
@@ -15056,12 +14554,6 @@
         <v/>
       </c>
       <c r="S45" t="str">
-        <v/>
-      </c>
-      <c r="T45" t="str">
-        <v/>
-      </c>
-      <c r="U45" t="str">
         <v/>
       </c>
     </row>
@@ -15082,13 +14574,13 @@
         <v>Shown</v>
       </c>
       <c r="F46" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G46" t="str">
         <v>Shown</v>
       </c>
       <c r="H46" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I46" t="str">
         <v>Hidden — group off</v>
@@ -15097,10 +14589,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K46" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L46" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M46" t="str">
         <v/>
@@ -15121,12 +14613,6 @@
         <v/>
       </c>
       <c r="S46" t="str">
-        <v/>
-      </c>
-      <c r="T46" t="str">
-        <v/>
-      </c>
-      <c r="U46" t="str">
         <v/>
       </c>
     </row>
@@ -15147,13 +14633,13 @@
         <v>Shown</v>
       </c>
       <c r="F47" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G47" t="str">
         <v>Shown</v>
       </c>
       <c r="H47" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I47" t="str">
         <v>Hidden — group off</v>
@@ -15162,10 +14648,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K47" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L47" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M47" t="str">
         <v/>
@@ -15186,12 +14672,6 @@
         <v/>
       </c>
       <c r="S47" t="str">
-        <v/>
-      </c>
-      <c r="T47" t="str">
-        <v/>
-      </c>
-      <c r="U47" t="str">
         <v/>
       </c>
     </row>
@@ -15212,13 +14692,13 @@
         <v>Shown</v>
       </c>
       <c r="F48" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G48" t="str">
         <v>Shown</v>
       </c>
       <c r="H48" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I48" t="str">
         <v>Hidden — group off</v>
@@ -15227,10 +14707,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K48" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L48" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M48" t="str">
         <v/>
@@ -15251,12 +14731,6 @@
         <v/>
       </c>
       <c r="S48" t="str">
-        <v/>
-      </c>
-      <c r="T48" t="str">
-        <v/>
-      </c>
-      <c r="U48" t="str">
         <v/>
       </c>
     </row>
@@ -15277,13 +14751,13 @@
         <v>Shown</v>
       </c>
       <c r="F49" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G49" t="str">
         <v>Shown</v>
       </c>
       <c r="H49" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I49" t="str">
         <v>Hidden — group off</v>
@@ -15292,10 +14766,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K49" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L49" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M49" t="str">
         <v/>
@@ -15316,12 +14790,6 @@
         <v/>
       </c>
       <c r="S49" t="str">
-        <v/>
-      </c>
-      <c r="T49" t="str">
-        <v/>
-      </c>
-      <c r="U49" t="str">
         <v/>
       </c>
     </row>
@@ -15342,13 +14810,13 @@
         <v>Shown</v>
       </c>
       <c r="F50" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G50" t="str">
         <v>Shown</v>
       </c>
       <c r="H50" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I50" t="str">
         <v>Hidden — group off</v>
@@ -15357,10 +14825,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K50" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L50" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -15381,12 +14849,6 @@
         <v/>
       </c>
       <c r="S50" t="str">
-        <v/>
-      </c>
-      <c r="T50" t="str">
-        <v/>
-      </c>
-      <c r="U50" t="str">
         <v/>
       </c>
     </row>
@@ -15407,13 +14869,13 @@
         <v>Shown</v>
       </c>
       <c r="F51" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G51" t="str">
         <v>Shown</v>
       </c>
       <c r="H51" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I51" t="str">
         <v>Hidden — group off</v>
@@ -15422,10 +14884,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K51" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L51" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -15446,12 +14908,6 @@
         <v/>
       </c>
       <c r="S51" t="str">
-        <v/>
-      </c>
-      <c r="T51" t="str">
-        <v/>
-      </c>
-      <c r="U51" t="str">
         <v/>
       </c>
     </row>
@@ -15472,13 +14928,13 @@
         <v>Shown</v>
       </c>
       <c r="F52" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G52" t="str">
         <v>Shown</v>
       </c>
       <c r="H52" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I52" t="str">
         <v>Hidden — group off</v>
@@ -15487,10 +14943,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K52" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L52" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -15511,12 +14967,6 @@
         <v/>
       </c>
       <c r="S52" t="str">
-        <v/>
-      </c>
-      <c r="T52" t="str">
-        <v/>
-      </c>
-      <c r="U52" t="str">
         <v/>
       </c>
     </row>
@@ -15537,13 +14987,13 @@
         <v>Shown</v>
       </c>
       <c r="F53" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G53" t="str">
         <v>Shown</v>
       </c>
       <c r="H53" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I53" t="str">
         <v>Hidden — group off</v>
@@ -15552,10 +15002,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K53" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L53" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -15576,12 +15026,6 @@
         <v/>
       </c>
       <c r="S53" t="str">
-        <v/>
-      </c>
-      <c r="T53" t="str">
-        <v/>
-      </c>
-      <c r="U53" t="str">
         <v/>
       </c>
     </row>
@@ -15602,13 +15046,13 @@
         <v>Shown</v>
       </c>
       <c r="F54" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G54" t="str">
         <v>Shown</v>
       </c>
       <c r="H54" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I54" t="str">
         <v>Hidden — group off</v>
@@ -15617,10 +15061,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K54" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L54" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -15641,12 +15085,6 @@
         <v/>
       </c>
       <c r="S54" t="str">
-        <v/>
-      </c>
-      <c r="T54" t="str">
-        <v/>
-      </c>
-      <c r="U54" t="str">
         <v/>
       </c>
     </row>
@@ -15667,13 +15105,13 @@
         <v>Shown</v>
       </c>
       <c r="F55" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G55" t="str">
         <v>Shown</v>
       </c>
       <c r="H55" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I55" t="str">
         <v>Hidden — group off</v>
@@ -15682,10 +15120,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K55" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L55" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M55" t="str">
         <v/>
@@ -15706,12 +15144,6 @@
         <v/>
       </c>
       <c r="S55" t="str">
-        <v/>
-      </c>
-      <c r="T55" t="str">
-        <v/>
-      </c>
-      <c r="U55" t="str">
         <v/>
       </c>
     </row>
@@ -15747,10 +15179,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K56" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L56" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M56" t="str">
         <v/>
@@ -15771,12 +15203,6 @@
         <v/>
       </c>
       <c r="S56" t="str">
-        <v/>
-      </c>
-      <c r="T56" t="str">
-        <v/>
-      </c>
-      <c r="U56" t="str">
         <v/>
       </c>
     </row>
@@ -15812,10 +15238,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K57" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L57" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M57" t="str">
         <v/>
@@ -15836,12 +15262,6 @@
         <v/>
       </c>
       <c r="S57" t="str">
-        <v/>
-      </c>
-      <c r="T57" t="str">
-        <v/>
-      </c>
-      <c r="U57" t="str">
         <v/>
       </c>
     </row>
@@ -15874,13 +15294,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J58" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K58" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L58" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M58" t="str">
         <v/>
@@ -15901,12 +15321,6 @@
         <v/>
       </c>
       <c r="S58" t="str">
-        <v/>
-      </c>
-      <c r="T58" t="str">
-        <v/>
-      </c>
-      <c r="U58" t="str">
         <v/>
       </c>
     </row>
@@ -15939,13 +15353,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J59" t="str">
+        <v>Hidden — group off</v>
+      </c>
+      <c r="K59" t="str">
         <v>Hidden — no rate</v>
       </c>
-      <c r="K59" t="str">
-        <v>Hidden — group off</v>
-      </c>
       <c r="L59" t="str">
-        <v>Hidden — no rate</v>
+        <v/>
       </c>
       <c r="M59" t="str">
         <v/>
@@ -15966,12 +15380,6 @@
         <v/>
       </c>
       <c r="S59" t="str">
-        <v/>
-      </c>
-      <c r="T59" t="str">
-        <v/>
-      </c>
-      <c r="U59" t="str">
         <v/>
       </c>
     </row>
@@ -16004,13 +15412,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J60" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K60" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L60" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M60" t="str">
         <v/>
@@ -16031,12 +15439,6 @@
         <v/>
       </c>
       <c r="S60" t="str">
-        <v/>
-      </c>
-      <c r="T60" t="str">
-        <v/>
-      </c>
-      <c r="U60" t="str">
         <v/>
       </c>
     </row>
@@ -16075,7 +15477,7 @@
         <v>n/a — folded</v>
       </c>
       <c r="L61" t="str">
-        <v>n/a — folded</v>
+        <v/>
       </c>
       <c r="M61" t="str">
         <v/>
@@ -16096,12 +15498,6 @@
         <v/>
       </c>
       <c r="S61" t="str">
-        <v/>
-      </c>
-      <c r="T61" t="str">
-        <v/>
-      </c>
-      <c r="U61" t="str">
         <v/>
       </c>
     </row>
@@ -16134,13 +15530,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J62" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K62" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L62" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M62" t="str">
         <v/>
@@ -16161,12 +15557,6 @@
         <v/>
       </c>
       <c r="S62" t="str">
-        <v/>
-      </c>
-      <c r="T62" t="str">
-        <v/>
-      </c>
-      <c r="U62" t="str">
         <v/>
       </c>
     </row>
@@ -16199,13 +15589,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J63" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K63" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L63" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M63" t="str">
         <v/>
@@ -16226,12 +15616,6 @@
         <v/>
       </c>
       <c r="S63" t="str">
-        <v/>
-      </c>
-      <c r="T63" t="str">
-        <v/>
-      </c>
-      <c r="U63" t="str">
         <v/>
       </c>
     </row>
@@ -16270,7 +15654,7 @@
         <v>n/a — folded</v>
       </c>
       <c r="L64" t="str">
-        <v>n/a — folded</v>
+        <v/>
       </c>
       <c r="M64" t="str">
         <v/>
@@ -16291,12 +15675,6 @@
         <v/>
       </c>
       <c r="S64" t="str">
-        <v/>
-      </c>
-      <c r="T64" t="str">
-        <v/>
-      </c>
-      <c r="U64" t="str">
         <v/>
       </c>
     </row>
@@ -16329,13 +15707,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J65" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K65" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L65" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M65" t="str">
         <v/>
@@ -16356,12 +15734,6 @@
         <v/>
       </c>
       <c r="S65" t="str">
-        <v/>
-      </c>
-      <c r="T65" t="str">
-        <v/>
-      </c>
-      <c r="U65" t="str">
         <v/>
       </c>
     </row>
@@ -16394,13 +15766,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J66" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K66" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L66" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M66" t="str">
         <v/>
@@ -16421,12 +15793,6 @@
         <v/>
       </c>
       <c r="S66" t="str">
-        <v/>
-      </c>
-      <c r="T66" t="str">
-        <v/>
-      </c>
-      <c r="U66" t="str">
         <v/>
       </c>
     </row>
@@ -16459,13 +15825,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J67" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K67" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L67" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M67" t="str">
         <v/>
@@ -16486,12 +15852,6 @@
         <v/>
       </c>
       <c r="S67" t="str">
-        <v/>
-      </c>
-      <c r="T67" t="str">
-        <v/>
-      </c>
-      <c r="U67" t="str">
         <v/>
       </c>
     </row>
@@ -16530,7 +15890,7 @@
         <v>n/a — folded</v>
       </c>
       <c r="L68" t="str">
-        <v>n/a — folded</v>
+        <v/>
       </c>
       <c r="M68" t="str">
         <v/>
@@ -16551,12 +15911,6 @@
         <v/>
       </c>
       <c r="S68" t="str">
-        <v/>
-      </c>
-      <c r="T68" t="str">
-        <v/>
-      </c>
-      <c r="U68" t="str">
         <v/>
       </c>
     </row>
@@ -16577,25 +15931,25 @@
         <v>Hidden — no rate</v>
       </c>
       <c r="F69" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G69" t="str">
         <v>Shown</v>
       </c>
       <c r="H69" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I69" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J69" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K69" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L69" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M69" t="str">
         <v/>
@@ -16616,12 +15970,6 @@
         <v/>
       </c>
       <c r="S69" t="str">
-        <v/>
-      </c>
-      <c r="T69" t="str">
-        <v/>
-      </c>
-      <c r="U69" t="str">
         <v/>
       </c>
     </row>
@@ -16642,25 +15990,25 @@
         <v>Hidden — no rate</v>
       </c>
       <c r="F70" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G70" t="str">
         <v>Shown</v>
       </c>
       <c r="H70" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I70" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J70" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K70" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L70" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M70" t="str">
         <v/>
@@ -16681,12 +16029,6 @@
         <v/>
       </c>
       <c r="S70" t="str">
-        <v/>
-      </c>
-      <c r="T70" t="str">
-        <v/>
-      </c>
-      <c r="U70" t="str">
         <v/>
       </c>
     </row>
@@ -16719,13 +16061,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J71" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K71" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L71" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M71" t="str">
         <v/>
@@ -16746,12 +16088,6 @@
         <v/>
       </c>
       <c r="S71" t="str">
-        <v/>
-      </c>
-      <c r="T71" t="str">
-        <v/>
-      </c>
-      <c r="U71" t="str">
         <v/>
       </c>
     </row>
@@ -16784,13 +16120,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J72" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K72" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L72" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M72" t="str">
         <v/>
@@ -16811,12 +16147,6 @@
         <v/>
       </c>
       <c r="S72" t="str">
-        <v/>
-      </c>
-      <c r="T72" t="str">
-        <v/>
-      </c>
-      <c r="U72" t="str">
         <v/>
       </c>
     </row>
@@ -16849,13 +16179,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J73" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K73" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L73" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M73" t="str">
         <v/>
@@ -16876,12 +16206,6 @@
         <v/>
       </c>
       <c r="S73" t="str">
-        <v/>
-      </c>
-      <c r="T73" t="str">
-        <v/>
-      </c>
-      <c r="U73" t="str">
         <v/>
       </c>
     </row>
@@ -16914,13 +16238,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J74" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K74" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L74" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M74" t="str">
         <v/>
@@ -16941,12 +16265,6 @@
         <v/>
       </c>
       <c r="S74" t="str">
-        <v/>
-      </c>
-      <c r="T74" t="str">
-        <v/>
-      </c>
-      <c r="U74" t="str">
         <v/>
       </c>
     </row>
@@ -16979,13 +16297,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J75" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K75" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L75" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M75" t="str">
         <v/>
@@ -17006,12 +16324,6 @@
         <v/>
       </c>
       <c r="S75" t="str">
-        <v/>
-      </c>
-      <c r="T75" t="str">
-        <v/>
-      </c>
-      <c r="U75" t="str">
         <v/>
       </c>
     </row>
@@ -17044,13 +16356,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J76" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K76" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L76" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M76" t="str">
         <v/>
@@ -17071,12 +16383,6 @@
         <v/>
       </c>
       <c r="S76" t="str">
-        <v/>
-      </c>
-      <c r="T76" t="str">
-        <v/>
-      </c>
-      <c r="U76" t="str">
         <v/>
       </c>
     </row>
@@ -17109,13 +16415,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J77" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K77" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L77" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M77" t="str">
         <v/>
@@ -17136,12 +16442,6 @@
         <v/>
       </c>
       <c r="S77" t="str">
-        <v/>
-      </c>
-      <c r="T77" t="str">
-        <v/>
-      </c>
-      <c r="U77" t="str">
         <v/>
       </c>
     </row>
@@ -17174,13 +16474,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J78" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K78" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L78" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M78" t="str">
         <v/>
@@ -17201,12 +16501,6 @@
         <v/>
       </c>
       <c r="S78" t="str">
-        <v/>
-      </c>
-      <c r="T78" t="str">
-        <v/>
-      </c>
-      <c r="U78" t="str">
         <v/>
       </c>
     </row>
@@ -17239,13 +16533,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J79" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K79" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L79" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M79" t="str">
         <v/>
@@ -17266,12 +16560,6 @@
         <v/>
       </c>
       <c r="S79" t="str">
-        <v/>
-      </c>
-      <c r="T79" t="str">
-        <v/>
-      </c>
-      <c r="U79" t="str">
         <v/>
       </c>
     </row>
@@ -17304,13 +16592,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J80" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K80" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L80" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M80" t="str">
         <v/>
@@ -17331,12 +16619,6 @@
         <v/>
       </c>
       <c r="S80" t="str">
-        <v/>
-      </c>
-      <c r="T80" t="str">
-        <v/>
-      </c>
-      <c r="U80" t="str">
         <v/>
       </c>
     </row>
@@ -17369,13 +16651,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J81" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K81" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L81" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M81" t="str">
         <v/>
@@ -17396,12 +16678,6 @@
         <v/>
       </c>
       <c r="S81" t="str">
-        <v/>
-      </c>
-      <c r="T81" t="str">
-        <v/>
-      </c>
-      <c r="U81" t="str">
         <v/>
       </c>
     </row>
@@ -17434,13 +16710,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J82" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K82" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L82" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M82" t="str">
         <v/>
@@ -17461,12 +16737,6 @@
         <v/>
       </c>
       <c r="S82" t="str">
-        <v/>
-      </c>
-      <c r="T82" t="str">
-        <v/>
-      </c>
-      <c r="U82" t="str">
         <v/>
       </c>
     </row>
@@ -17499,13 +16769,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J83" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K83" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L83" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M83" t="str">
         <v/>
@@ -17526,12 +16796,6 @@
         <v/>
       </c>
       <c r="S83" t="str">
-        <v/>
-      </c>
-      <c r="T83" t="str">
-        <v/>
-      </c>
-      <c r="U83" t="str">
         <v/>
       </c>
     </row>
@@ -17552,25 +16816,25 @@
         <v>Shown</v>
       </c>
       <c r="F84" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G84" t="str">
         <v>Shown</v>
       </c>
       <c r="H84" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I84" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J84" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K84" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L84" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M84" t="str">
         <v/>
@@ -17591,12 +16855,6 @@
         <v/>
       </c>
       <c r="S84" t="str">
-        <v/>
-      </c>
-      <c r="T84" t="str">
-        <v/>
-      </c>
-      <c r="U84" t="str">
         <v/>
       </c>
     </row>
@@ -17617,25 +16875,25 @@
         <v>Shown</v>
       </c>
       <c r="F85" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G85" t="str">
         <v>Shown</v>
       </c>
       <c r="H85" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I85" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J85" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K85" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L85" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M85" t="str">
         <v/>
@@ -17656,12 +16914,6 @@
         <v/>
       </c>
       <c r="S85" t="str">
-        <v/>
-      </c>
-      <c r="T85" t="str">
-        <v/>
-      </c>
-      <c r="U85" t="str">
         <v/>
       </c>
     </row>
@@ -17682,25 +16934,25 @@
         <v>Shown</v>
       </c>
       <c r="F86" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G86" t="str">
         <v>Shown</v>
       </c>
       <c r="H86" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I86" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J86" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K86" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L86" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M86" t="str">
         <v/>
@@ -17721,12 +16973,6 @@
         <v/>
       </c>
       <c r="S86" t="str">
-        <v/>
-      </c>
-      <c r="T86" t="str">
-        <v/>
-      </c>
-      <c r="U86" t="str">
         <v/>
       </c>
     </row>
@@ -17747,25 +16993,25 @@
         <v>Shown</v>
       </c>
       <c r="F87" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G87" t="str">
         <v>Shown</v>
       </c>
       <c r="H87" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I87" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J87" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K87" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L87" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M87" t="str">
         <v/>
@@ -17786,12 +17032,6 @@
         <v/>
       </c>
       <c r="S87" t="str">
-        <v/>
-      </c>
-      <c r="T87" t="str">
-        <v/>
-      </c>
-      <c r="U87" t="str">
         <v/>
       </c>
     </row>
@@ -17812,25 +17052,25 @@
         <v>Shown</v>
       </c>
       <c r="F88" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G88" t="str">
         <v>Shown</v>
       </c>
       <c r="H88" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I88" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J88" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K88" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L88" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M88" t="str">
         <v/>
@@ -17851,12 +17091,6 @@
         <v/>
       </c>
       <c r="S88" t="str">
-        <v/>
-      </c>
-      <c r="T88" t="str">
-        <v/>
-      </c>
-      <c r="U88" t="str">
         <v/>
       </c>
     </row>
@@ -17877,25 +17111,25 @@
         <v>Shown</v>
       </c>
       <c r="F89" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G89" t="str">
         <v>Shown</v>
       </c>
       <c r="H89" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I89" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J89" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K89" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L89" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M89" t="str">
         <v/>
@@ -17916,12 +17150,6 @@
         <v/>
       </c>
       <c r="S89" t="str">
-        <v/>
-      </c>
-      <c r="T89" t="str">
-        <v/>
-      </c>
-      <c r="U89" t="str">
         <v/>
       </c>
     </row>
@@ -17942,25 +17170,25 @@
         <v>Shown</v>
       </c>
       <c r="F90" t="str">
-        <v>Shown</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G90" t="str">
         <v>Shown</v>
       </c>
       <c r="H90" t="str">
-        <v>Hidden — no rate</v>
+        <v>Shown</v>
       </c>
       <c r="I90" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="J90" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K90" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L90" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M90" t="str">
         <v/>
@@ -17981,12 +17209,6 @@
         <v/>
       </c>
       <c r="S90" t="str">
-        <v/>
-      </c>
-      <c r="T90" t="str">
-        <v/>
-      </c>
-      <c r="U90" t="str">
         <v/>
       </c>
     </row>
@@ -18019,13 +17241,13 @@
         <v>Hidden — group off</v>
       </c>
       <c r="J91" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K91" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L91" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M91" t="str">
         <v/>
@@ -18046,12 +17268,6 @@
         <v/>
       </c>
       <c r="S91" t="str">
-        <v/>
-      </c>
-      <c r="T91" t="str">
-        <v/>
-      </c>
-      <c r="U91" t="str">
         <v/>
       </c>
     </row>
@@ -18072,13 +17288,13 @@
         <v>Shown</v>
       </c>
       <c r="F92" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="G92" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="H92" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I92" t="str">
         <v>Hidden — group off</v>
@@ -18087,10 +17303,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K92" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L92" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M92" t="str">
         <v/>
@@ -18111,12 +17327,6 @@
         <v/>
       </c>
       <c r="S92" t="str">
-        <v/>
-      </c>
-      <c r="T92" t="str">
-        <v/>
-      </c>
-      <c r="U92" t="str">
         <v/>
       </c>
     </row>
@@ -18137,13 +17347,13 @@
         <v>Shown</v>
       </c>
       <c r="F93" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="G93" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="H93" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I93" t="str">
         <v>Hidden — group off</v>
@@ -18152,10 +17362,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K93" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L93" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M93" t="str">
         <v/>
@@ -18176,12 +17386,6 @@
         <v/>
       </c>
       <c r="S93" t="str">
-        <v/>
-      </c>
-      <c r="T93" t="str">
-        <v/>
-      </c>
-      <c r="U93" t="str">
         <v/>
       </c>
     </row>
@@ -18202,13 +17406,13 @@
         <v>Shown</v>
       </c>
       <c r="F94" t="str">
-        <v>Hidden — group off</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G94" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="H94" t="str">
-        <v>Hidden — no rate</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I94" t="str">
         <v>Hidden — group off</v>
@@ -18217,10 +17421,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K94" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L94" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M94" t="str">
         <v/>
@@ -18241,12 +17445,6 @@
         <v/>
       </c>
       <c r="S94" t="str">
-        <v/>
-      </c>
-      <c r="T94" t="str">
-        <v/>
-      </c>
-      <c r="U94" t="str">
         <v/>
       </c>
     </row>
@@ -18267,13 +17465,13 @@
         <v>Shown</v>
       </c>
       <c r="F95" t="str">
-        <v>Hidden — group off</v>
+        <v>Hidden — no rate</v>
       </c>
       <c r="G95" t="str">
         <v>Hidden — group off</v>
       </c>
       <c r="H95" t="str">
-        <v>Hidden — no rate</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I95" t="str">
         <v>Hidden — group off</v>
@@ -18282,10 +17480,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K95" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L95" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M95" t="str">
         <v/>
@@ -18306,12 +17504,6 @@
         <v/>
       </c>
       <c r="S95" t="str">
-        <v/>
-      </c>
-      <c r="T95" t="str">
-        <v/>
-      </c>
-      <c r="U95" t="str">
         <v/>
       </c>
     </row>
@@ -18335,10 +17527,10 @@
         <v>Shown</v>
       </c>
       <c r="G96" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H96" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I96" t="str">
         <v>Hidden — group off</v>
@@ -18347,10 +17539,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K96" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L96" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M96" t="str">
         <v/>
@@ -18371,12 +17563,6 @@
         <v/>
       </c>
       <c r="S96" t="str">
-        <v/>
-      </c>
-      <c r="T96" t="str">
-        <v/>
-      </c>
-      <c r="U96" t="str">
         <v/>
       </c>
     </row>
@@ -18400,10 +17586,10 @@
         <v>Shown</v>
       </c>
       <c r="G97" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H97" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I97" t="str">
         <v>Hidden — group off</v>
@@ -18412,10 +17598,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K97" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L97" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M97" t="str">
         <v/>
@@ -18436,12 +17622,6 @@
         <v/>
       </c>
       <c r="S97" t="str">
-        <v/>
-      </c>
-      <c r="T97" t="str">
-        <v/>
-      </c>
-      <c r="U97" t="str">
         <v/>
       </c>
     </row>
@@ -18465,10 +17645,10 @@
         <v>Shown</v>
       </c>
       <c r="G98" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H98" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I98" t="str">
         <v>Hidden — group off</v>
@@ -18477,10 +17657,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K98" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L98" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M98" t="str">
         <v/>
@@ -18501,12 +17681,6 @@
         <v/>
       </c>
       <c r="S98" t="str">
-        <v/>
-      </c>
-      <c r="T98" t="str">
-        <v/>
-      </c>
-      <c r="U98" t="str">
         <v/>
       </c>
     </row>
@@ -18530,10 +17704,10 @@
         <v>Shown</v>
       </c>
       <c r="G99" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H99" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I99" t="str">
         <v>Hidden — group off</v>
@@ -18542,10 +17716,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K99" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L99" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M99" t="str">
         <v/>
@@ -18566,12 +17740,6 @@
         <v/>
       </c>
       <c r="S99" t="str">
-        <v/>
-      </c>
-      <c r="T99" t="str">
-        <v/>
-      </c>
-      <c r="U99" t="str">
         <v/>
       </c>
     </row>
@@ -18595,10 +17763,10 @@
         <v>Shown</v>
       </c>
       <c r="G100" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H100" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I100" t="str">
         <v>Hidden — group off</v>
@@ -18607,10 +17775,10 @@
         <v>Hidden — group off</v>
       </c>
       <c r="K100" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L100" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M100" t="str">
         <v/>
@@ -18631,12 +17799,6 @@
         <v/>
       </c>
       <c r="S100" t="str">
-        <v/>
-      </c>
-      <c r="T100" t="str">
-        <v/>
-      </c>
-      <c r="U100" t="str">
         <v/>
       </c>
     </row>
@@ -18660,22 +17822,22 @@
         <v>Shown</v>
       </c>
       <c r="G101" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H101" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I101" t="str">
         <v>Shown</v>
       </c>
       <c r="J101" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K101" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L101" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M101" t="str">
         <v/>
@@ -18696,12 +17858,6 @@
         <v/>
       </c>
       <c r="S101" t="str">
-        <v/>
-      </c>
-      <c r="T101" t="str">
-        <v/>
-      </c>
-      <c r="U101" t="str">
         <v/>
       </c>
     </row>
@@ -18725,22 +17881,22 @@
         <v>Shown</v>
       </c>
       <c r="G102" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H102" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I102" t="str">
         <v>Shown</v>
       </c>
       <c r="J102" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K102" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L102" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M102" t="str">
         <v/>
@@ -18761,12 +17917,6 @@
         <v/>
       </c>
       <c r="S102" t="str">
-        <v/>
-      </c>
-      <c r="T102" t="str">
-        <v/>
-      </c>
-      <c r="U102" t="str">
         <v/>
       </c>
     </row>
@@ -18790,22 +17940,22 @@
         <v>Shown</v>
       </c>
       <c r="G103" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H103" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I103" t="str">
         <v>Shown</v>
       </c>
       <c r="J103" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K103" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L103" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M103" t="str">
         <v/>
@@ -18826,12 +17976,6 @@
         <v/>
       </c>
       <c r="S103" t="str">
-        <v/>
-      </c>
-      <c r="T103" t="str">
-        <v/>
-      </c>
-      <c r="U103" t="str">
         <v/>
       </c>
     </row>
@@ -18855,22 +17999,22 @@
         <v>Shown</v>
       </c>
       <c r="G104" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H104" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I104" t="str">
         <v>Shown</v>
       </c>
       <c r="J104" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K104" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L104" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M104" t="str">
         <v/>
@@ -18891,12 +18035,6 @@
         <v/>
       </c>
       <c r="S104" t="str">
-        <v/>
-      </c>
-      <c r="T104" t="str">
-        <v/>
-      </c>
-      <c r="U104" t="str">
         <v/>
       </c>
     </row>
@@ -18920,22 +18058,22 @@
         <v>Shown</v>
       </c>
       <c r="G105" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H105" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I105" t="str">
         <v>Shown</v>
       </c>
       <c r="J105" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K105" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L105" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M105" t="str">
         <v/>
@@ -18956,12 +18094,6 @@
         <v/>
       </c>
       <c r="S105" t="str">
-        <v/>
-      </c>
-      <c r="T105" t="str">
-        <v/>
-      </c>
-      <c r="U105" t="str">
         <v/>
       </c>
     </row>
@@ -18985,22 +18117,22 @@
         <v>Shown</v>
       </c>
       <c r="G106" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H106" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I106" t="str">
         <v>Shown</v>
       </c>
       <c r="J106" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K106" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L106" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M106" t="str">
         <v/>
@@ -19021,12 +18153,6 @@
         <v/>
       </c>
       <c r="S106" t="str">
-        <v/>
-      </c>
-      <c r="T106" t="str">
-        <v/>
-      </c>
-      <c r="U106" t="str">
         <v/>
       </c>
     </row>
@@ -19050,22 +18176,22 @@
         <v>Shown</v>
       </c>
       <c r="G107" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H107" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I107" t="str">
         <v>Shown</v>
       </c>
       <c r="J107" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K107" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L107" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M107" t="str">
         <v/>
@@ -19086,12 +18212,6 @@
         <v/>
       </c>
       <c r="S107" t="str">
-        <v/>
-      </c>
-      <c r="T107" t="str">
-        <v/>
-      </c>
-      <c r="U107" t="str">
         <v/>
       </c>
     </row>
@@ -19115,22 +18235,22 @@
         <v>Shown</v>
       </c>
       <c r="G108" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H108" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I108" t="str">
         <v>Shown</v>
       </c>
       <c r="J108" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K108" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L108" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M108" t="str">
         <v/>
@@ -19151,12 +18271,6 @@
         <v/>
       </c>
       <c r="S108" t="str">
-        <v/>
-      </c>
-      <c r="T108" t="str">
-        <v/>
-      </c>
-      <c r="U108" t="str">
         <v/>
       </c>
     </row>
@@ -19180,22 +18294,22 @@
         <v>Shown</v>
       </c>
       <c r="G109" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H109" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I109" t="str">
         <v>Shown</v>
       </c>
       <c r="J109" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K109" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L109" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M109" t="str">
         <v/>
@@ -19216,12 +18330,6 @@
         <v/>
       </c>
       <c r="S109" t="str">
-        <v/>
-      </c>
-      <c r="T109" t="str">
-        <v/>
-      </c>
-      <c r="U109" t="str">
         <v/>
       </c>
     </row>
@@ -19242,25 +18350,25 @@
         <v>Shown</v>
       </c>
       <c r="F110" t="str">
+        <v>Shown</v>
+      </c>
+      <c r="G110" t="str">
         <v>Hidden — no rate</v>
       </c>
-      <c r="G110" t="str">
-        <v>Hidden — group off</v>
-      </c>
       <c r="H110" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I110" t="str">
         <v>Shown</v>
       </c>
       <c r="J110" t="str">
-        <v>Hidden — no rate</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K110" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L110" t="str">
-        <v>Hidden — no rate</v>
+        <v/>
       </c>
       <c r="M110" t="str">
         <v/>
@@ -19281,12 +18389,6 @@
         <v/>
       </c>
       <c r="S110" t="str">
-        <v/>
-      </c>
-      <c r="T110" t="str">
-        <v/>
-      </c>
-      <c r="U110" t="str">
         <v/>
       </c>
     </row>
@@ -19310,22 +18412,22 @@
         <v>Shown</v>
       </c>
       <c r="G111" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H111" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I111" t="str">
         <v>Shown</v>
       </c>
       <c r="J111" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K111" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L111" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M111" t="str">
         <v/>
@@ -19346,12 +18448,6 @@
         <v/>
       </c>
       <c r="S111" t="str">
-        <v/>
-      </c>
-      <c r="T111" t="str">
-        <v/>
-      </c>
-      <c r="U111" t="str">
         <v/>
       </c>
     </row>
@@ -19375,22 +18471,22 @@
         <v>Shown</v>
       </c>
       <c r="G112" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H112" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I112" t="str">
         <v>Shown</v>
       </c>
       <c r="J112" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K112" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L112" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M112" t="str">
         <v/>
@@ -19411,12 +18507,6 @@
         <v/>
       </c>
       <c r="S112" t="str">
-        <v/>
-      </c>
-      <c r="T112" t="str">
-        <v/>
-      </c>
-      <c r="U112" t="str">
         <v/>
       </c>
     </row>
@@ -19440,22 +18530,22 @@
         <v>Shown</v>
       </c>
       <c r="G113" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="H113" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="I113" t="str">
         <v>Hidden — no rate</v>
       </c>
       <c r="J113" t="str">
-        <v>Shown</v>
+        <v>Hidden — group off</v>
       </c>
       <c r="K113" t="str">
-        <v>Hidden — group off</v>
+        <v>Shown</v>
       </c>
       <c r="L113" t="str">
-        <v>Shown</v>
+        <v/>
       </c>
       <c r="M113" t="str">
         <v/>
@@ -19476,12 +18566,6 @@
         <v/>
       </c>
       <c r="S113" t="str">
-        <v/>
-      </c>
-      <c r="T113" t="str">
-        <v/>
-      </c>
-      <c r="U113" t="str">
         <v/>
       </c>
     </row>
@@ -19502,25 +18586,22 @@
         <v>98</v>
       </c>
       <c r="F115">
+        <v>76</v>
+      </c>
+      <c r="G115">
         <v>98</v>
       </c>
-      <c r="G115">
+      <c r="H115">
         <v>68</v>
-      </c>
-      <c r="H115">
-        <v>76</v>
       </c>
       <c r="I115">
         <v>15</v>
       </c>
       <c r="J115">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="K115">
-        <v>4</v>
-      </c>
-      <c r="L115">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116">
@@ -19540,25 +18621,22 @@
         <v>52</v>
       </c>
       <c r="F116">
+        <v>57</v>
+      </c>
+      <c r="G116">
         <v>55</v>
       </c>
-      <c r="G116">
+      <c r="H116">
         <v>25</v>
-      </c>
-      <c r="H116">
-        <v>57</v>
       </c>
       <c r="I116">
         <v>14</v>
       </c>
       <c r="J116">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K116">
-        <v>4</v>
-      </c>
-      <c r="L116">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="117">
@@ -19578,25 +18656,22 @@
         <v>52</v>
       </c>
       <c r="F117">
+        <v>57</v>
+      </c>
+      <c r="G117">
         <v>55</v>
       </c>
-      <c r="G117">
+      <c r="H117">
         <v>25</v>
-      </c>
-      <c r="H117">
-        <v>57</v>
       </c>
       <c r="I117">
         <v>14</v>
       </c>
       <c r="J117">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K117">
-        <v>4</v>
-      </c>
-      <c r="L117">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="118">
@@ -19616,25 +18691,22 @@
         <v>64</v>
       </c>
       <c r="F118">
+        <v>68</v>
+      </c>
+      <c r="G118">
         <v>67</v>
       </c>
-      <c r="G118">
+      <c r="H118">
         <v>37</v>
-      </c>
-      <c r="H118">
-        <v>68</v>
       </c>
       <c r="I118">
         <v>14</v>
       </c>
       <c r="J118">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K118">
-        <v>4</v>
-      </c>
-      <c r="L118">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="119">
@@ -19654,25 +18726,22 @@
         <v>69</v>
       </c>
       <c r="F119">
+        <v>66</v>
+      </c>
+      <c r="G119">
         <v>72</v>
       </c>
-      <c r="G119">
+      <c r="H119">
         <v>42</v>
-      </c>
-      <c r="H119">
-        <v>66</v>
       </c>
       <c r="I119">
         <v>14</v>
       </c>
       <c r="J119">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="K119">
-        <v>4</v>
-      </c>
-      <c r="L119">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="120">
@@ -19692,25 +18761,22 @@
         <v>70</v>
       </c>
       <c r="F120">
+        <v>66</v>
+      </c>
+      <c r="G120">
         <v>72</v>
       </c>
-      <c r="G120">
+      <c r="H120">
         <v>42</v>
-      </c>
-      <c r="H120">
-        <v>66</v>
       </c>
       <c r="I120">
         <v>14</v>
       </c>
       <c r="J120">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K120">
-        <v>4</v>
-      </c>
-      <c r="L120">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="121">
@@ -19730,25 +18796,22 @@
         <v>64</v>
       </c>
       <c r="F121">
+        <v>65</v>
+      </c>
+      <c r="G121">
         <v>67</v>
       </c>
-      <c r="G121">
+      <c r="H121">
         <v>37</v>
-      </c>
-      <c r="H121">
-        <v>65</v>
       </c>
       <c r="I121">
         <v>14</v>
       </c>
       <c r="J121">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K121">
-        <v>4</v>
-      </c>
-      <c r="L121">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="122">
@@ -19768,25 +18831,22 @@
         <v>71</v>
       </c>
       <c r="F122">
+        <v>67</v>
+      </c>
+      <c r="G122">
         <v>72</v>
       </c>
-      <c r="G122">
+      <c r="H122">
         <v>42</v>
-      </c>
-      <c r="H122">
-        <v>67</v>
       </c>
       <c r="I122">
         <v>15</v>
       </c>
       <c r="J122">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="K122">
-        <v>4</v>
-      </c>
-      <c r="L122">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123">
@@ -19806,30 +18866,27 @@
         <v>71</v>
       </c>
       <c r="F123">
+        <v>68</v>
+      </c>
+      <c r="G123">
         <v>75</v>
       </c>
-      <c r="G123">
+      <c r="H123">
         <v>45</v>
-      </c>
-      <c r="H123">
-        <v>68</v>
       </c>
       <c r="I123">
         <v>14</v>
       </c>
       <c r="J123">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="K123">
-        <v>4</v>
-      </c>
-      <c r="L123">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U123"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S123"/>
   </ignoredErrors>
 </worksheet>
 </file>
